--- a/100kW_380V_Inverter/Driver/ADC_Comm/ADC_Comm/ADC_Comm_.xlsx
+++ b/100kW_380V_Inverter/Driver/ADC_Comm/ADC_Comm/ADC_Comm_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Inverters-in-development\100kW_380V_Inverter\Driver\ADC_Comm\ADC_Comm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63CF6E5F-70EB-40D3-A925-B4D08F7F1B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3682078-099E-4391-9F63-3BD145EB05ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1470" yWindow="1470" windowWidth="16200" windowHeight="9308" xr2:uid="{074F6D17-AAF2-42AD-A89B-08639642AE7A}"/>
   </bookViews>
@@ -544,7 +544,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -554,6 +554,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,12 +591,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1392,22 +1400,22 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="6">
         <v>1</v>
       </c>
     </row>
